--- a/data/gravel/Van Nicholas Nootau 2025.xlsx
+++ b/data/gravel/Van Nicholas Nootau 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E5AB2-5464-994E-9382-82A0E6E9FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A518D9-7B5E-0844-9347-4F2C9D4E6E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35320" yWindow="-26420" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32440" yWindow="-26420" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -275,9 +275,6 @@
     <t>Van Nicholas</t>
   </si>
   <si>
-    <t>Rowtag</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -417,6 +414,9 @@
   </si>
   <si>
     <t>https://shop.vannicholas.com/en/producten/front-forks/VNT-Front-fork-ADV-Full-Carbon-Adventure/28764</t>
+  </si>
+  <si>
+    <t>Nootau</t>
   </si>
 </sst>
 </file>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -800,12 +800,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -821,27 +821,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>83</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>84</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9">
         <v>17.5</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>444</v>
@@ -881,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11">
         <v>444</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12">
         <v>384</v>
@@ -921,7 +921,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13">
         <v>579</v>
@@ -938,10 +938,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14">
         <v>553</v>
@@ -961,7 +961,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>68.5</v>
@@ -981,7 +981,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16">
         <v>73.7</v>
@@ -1001,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17">
         <v>130</v>
@@ -1021,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18">
         <v>1130</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19">
         <v>673</v>
@@ -1061,7 +1061,7 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20">
         <v>70</v>
@@ -1081,7 +1081,7 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21">
         <v>465</v>
@@ -1101,7 +1101,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C22">
         <v>51</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23">
         <v>5.18</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24">
         <v>2.35</v>
@@ -1161,7 +1161,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>621</v>
@@ -1181,7 +1181,7 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C26">
         <v>398</v>
@@ -1201,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27">
         <v>769</v>
@@ -1254,7 +1254,7 @@
         <v>480</v>
       </c>
       <c r="G29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1312,7 +1312,7 @@
         <v>2.4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1364,7 +1364,7 @@
         <v>66</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1372,7 +1372,7 @@
         <v>67</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1396,7 +1396,7 @@
         <v>32</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1474,7 +1474,7 @@
         <v>76</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1482,7 +1482,7 @@
         <v>77</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1490,7 +1490,7 @@
         <v>78</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1498,7 +1498,7 @@
         <v>42</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1525,7 +1525,7 @@
         <v>46</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1553,7 +1553,7 @@
         <v>51</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -1653,7 +1653,7 @@
         <v>65</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1661,7 +1661,7 @@
         <v>72</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Van Nicholas Nootau 2025.xlsx
+++ b/data/gravel/Van Nicholas Nootau 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A518D9-7B5E-0844-9347-4F2C9D4E6E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433D3BF4-1F68-3D4B-8866-0DF27BF60BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-26420" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9840" yWindow="1140" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -404,9 +404,6 @@
     <t>frame_size_in</t>
   </si>
   <si>
-    <t>a8:f37</t>
-  </si>
-  <si>
     <t>tapered</t>
   </si>
   <si>
@@ -417,6 +414,15 @@
   </si>
   <si>
     <t>Nootau</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f39</t>
   </si>
 </sst>
 </file>
@@ -756,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -776,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -813,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1254,413 +1260,450 @@
         <v>480</v>
       </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>22</v>
+      <c r="A30" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>21</v>
+      <c r="A31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33">
-        <v>700</v>
-      </c>
-      <c r="D33">
-        <v>700</v>
-      </c>
-      <c r="E33">
-        <v>700</v>
-      </c>
-      <c r="F33">
-        <v>700</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34">
-        <v>2.4</v>
-      </c>
-      <c r="D34">
-        <v>2.4</v>
-      </c>
-      <c r="E34">
-        <v>2.4</v>
-      </c>
-      <c r="F34">
-        <v>2.4</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C35">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="D35">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="E35">
-        <v>2.8</v>
+        <v>700</v>
       </c>
       <c r="F35">
-        <v>2.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="C36">
+        <v>2.4</v>
+      </c>
+      <c r="D36">
+        <v>2.4</v>
+      </c>
+      <c r="E36">
+        <v>2.4</v>
+      </c>
+      <c r="F36">
+        <v>2.4</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C37">
+        <v>2.8</v>
+      </c>
+      <c r="D37">
+        <v>2.8</v>
+      </c>
+      <c r="E37">
+        <v>2.8</v>
+      </c>
+      <c r="F37">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>112</v>
+        <v>68</v>
+      </c>
+      <c r="B44" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46">
-        <v>2.8</v>
+        <v>32</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>40</v>
       </c>
-      <c r="B52">
+      <c r="B54">
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>41</v>
       </c>
-      <c r="B53">
+      <c r="B55">
         <v>110</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>76</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>78</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>44</v>
       </c>
-      <c r="B62">
+      <c r="B64">
         <v>31.6</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>45</v>
       </c>
-      <c r="B63" s="1"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>51</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>55</v>
       </c>
-      <c r="B73">
+      <c r="B75">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>56</v>
       </c>
-      <c r="B74">
+      <c r="B76">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>57</v>
       </c>
-      <c r="B75">
+      <c r="B77">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>58</v>
       </c>
-      <c r="B76">
+      <c r="B78">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>59</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>60</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>61</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>62</v>
-      </c>
-      <c r="B80">
-        <v>2399</v>
+        <v>60</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81">
-        <v>5349</v>
+        <v>61</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B82">
+        <v>2399</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>110</v>
+        <v>63</v>
+      </c>
+      <c r="B83">
+        <v>5349</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>72</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B86" t="s">
         <v>109</v>
       </c>
     </row>
